--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,27 +11,756 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="256">
   <si>
     <t/>
   </si>
   <si>
+    <t>10000352</t>
+  </si>
+  <si>
+    <t>ABC SG COCOPNDAN 460</t>
+  </si>
+  <si>
+    <t>FES03N</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10000688</t>
+  </si>
+  <si>
+    <t>COCA COLA 1500 ML</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10000689</t>
+  </si>
+  <si>
+    <t>SPRITE 1500 ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10000690</t>
+  </si>
+  <si>
+    <t>FANTA STRAWBERY 1500</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10000700</t>
+  </si>
+  <si>
+    <t>ABC SQSH ORNGE 425ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10000704</t>
+  </si>
+  <si>
+    <t>MARJAN COCOPANDAN425</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10000771</t>
+  </si>
+  <si>
+    <t>ABC SQUASH LECI 425</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10000772</t>
+  </si>
+  <si>
+    <t>MARJAN MELON 425ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10010933</t>
+  </si>
+  <si>
+    <t>MARJAN SYRP ORNG 375</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10010946</t>
+  </si>
+  <si>
+    <t>MARJAN SQ.CCOPD 375</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10032795</t>
+  </si>
+  <si>
+    <t>INDOFOOD SYR ORG 460</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10032797</t>
+  </si>
+  <si>
+    <t>INDOFOOD SYR CCP 460</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10036625</t>
+  </si>
+  <si>
+    <t>ABC SG MELON 460</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20005058</t>
+  </si>
+  <si>
+    <t>FANTA FRUIT PUNCH1.5</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20015819</t>
+  </si>
+  <si>
+    <t>INDOFOOD SYR MLN 460</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20019631</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK 1L</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20066299</t>
+  </si>
+  <si>
+    <t>MARJAN SQSH MLN 375</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20142239</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 1L</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20144280</t>
+  </si>
+  <si>
+    <t>FANTA LECI 1500ML</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>PT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10000133</t>
+  </si>
+  <si>
+    <t>KHONG GUAN MN ASS650</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>10000360</t>
+  </si>
+  <si>
+    <t>KHONG GUAN RED 1600G</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>10000734</t>
+  </si>
+  <si>
+    <t>NISSIN WFR CHOCO 570</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20010655</t>
+  </si>
+  <si>
+    <t>TANGO WFER CHOCO 220</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20015239</t>
+  </si>
+  <si>
+    <t>TANGO WAFER VNL 220</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20025285</t>
+  </si>
+  <si>
+    <t>GERY BUTER COKIS 300</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20030644</t>
+  </si>
+  <si>
+    <t>GERY EGG ROLL 210G</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20041251</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 226</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20053745</t>
+  </si>
+  <si>
+    <t>NABATI RCHOC WFR 226</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20074001</t>
+  </si>
+  <si>
+    <t>NEXTAR BROWNIES 126G</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20084959</t>
+  </si>
+  <si>
+    <t>GERY CHOCLTS DARK190</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20133606</t>
+  </si>
+  <si>
+    <t>GIZZI MILK WAFER240</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20140010</t>
+  </si>
+  <si>
+    <t>GIZZI MLK WFR MKC240</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20040511</t>
+  </si>
+  <si>
+    <t>NSSIN WFR CHO S/E200</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>20137532</t>
+  </si>
+  <si>
+    <t>TANGO WFR CHEESE 200</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>10000132</t>
+  </si>
+  <si>
+    <t>MONDE BT.COOKIES 454</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>10000730</t>
+  </si>
+  <si>
+    <t>ASTOR STICK CKLT 330</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>10000735</t>
+  </si>
+  <si>
+    <t>ROMA BISC KELAPA 345</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>10005166</t>
+  </si>
+  <si>
+    <t>FOX'S FRUITS 150G</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>10036928</t>
+  </si>
+  <si>
+    <t>MD.EGG ROLL MINI 300</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>20015928</t>
+  </si>
+  <si>
+    <t>HATARI BISCUIT 300G</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>20015929</t>
+  </si>
+  <si>
+    <t>HATARI BISC.ASS 650G</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>20018270</t>
+  </si>
+  <si>
+    <t>FOX'S BERRIES KLG150</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>20020625</t>
+  </si>
+  <si>
+    <t>G/T COOKIES 120G</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>20023805</t>
+  </si>
+  <si>
+    <t>INACO JELLY MINI 50S</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>20031552</t>
+  </si>
+  <si>
+    <t>GOOD FAMILY KLG 400G</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>20036130</t>
+  </si>
+  <si>
+    <t>ROCHO WFR BOLA 300G</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>20036135</t>
+  </si>
+  <si>
+    <t>IDM WAFER STICK 450G</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>20069566</t>
+  </si>
+  <si>
+    <t>HOCK GUAN BISC.1350G</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>20069567</t>
+  </si>
+  <si>
+    <t>CORONATION BISC.450G</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>20074004</t>
+  </si>
+  <si>
+    <t>BORNEO BISC KLG 300G</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>20076737</t>
+  </si>
+  <si>
+    <t>SERENA CHS COOK 454G</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>20084963</t>
+  </si>
+  <si>
+    <t>KG WAFER STK CHO 500</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>20094206</t>
+  </si>
+  <si>
+    <t>ROMA WAFELLO CHO 234</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>20102838</t>
+  </si>
+  <si>
+    <t>MONDE SLCT BISC 800G</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>20103665</t>
+  </si>
+  <si>
+    <t>KINO NASTAR PNPL120</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>20112474</t>
+  </si>
+  <si>
+    <t>NISSIN WALEN BIS600G</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>20112570</t>
+  </si>
+  <si>
+    <t>KOKOLA C/BUTTER 288</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>20112571</t>
+  </si>
+  <si>
+    <t>KOKOLA C/COCONUT 288</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>20112572</t>
+  </si>
+  <si>
+    <t>KOKOLA C/CHOCO 288G</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>20119647</t>
+  </si>
+  <si>
+    <t>RIA RIO CRM VNLA 400</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>20119648</t>
+  </si>
+  <si>
+    <t>ROMA WFLO B.CRML 228</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>20125797</t>
+  </si>
+  <si>
+    <t>CHO2 WR SMPRG K/W270</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>20127567</t>
+  </si>
+  <si>
+    <t>ROYAL/C COOKIES 240G</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>20133029</t>
+  </si>
+  <si>
+    <t>TANGO WFL CHO HZL150</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>20133030</t>
+  </si>
+  <si>
+    <t>ROMA ARDEN CHOCO 216</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>20133031</t>
+  </si>
+  <si>
+    <t>IMPERIAL ASSRTD 144G</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>20136760</t>
+  </si>
+  <si>
+    <t>ROMA SANDW CKLT 300G</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>20140008</t>
+  </si>
+  <si>
+    <t>OREO SPC FAMILY213.2</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>20143784</t>
+  </si>
+  <si>
+    <t>DELBIS DLCA C/CHO152</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>20143861</t>
+  </si>
+  <si>
+    <t>G/T MLK MCA DIP120.7</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>20140953</t>
+  </si>
+  <si>
+    <t>P100 BCKT COK K/H240</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>20143575</t>
+  </si>
+  <si>
+    <t>P100 BCKT KRM MD200</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>20133363</t>
+  </si>
+  <si>
+    <t>TANGO WFR MLK CHO220</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>10020713</t>
+  </si>
+  <si>
+    <t>WG COCO CUBE CP 1KG</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>10021003</t>
+  </si>
+  <si>
+    <t>W/COCO CCPD SLC 1KG</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>10038354</t>
+  </si>
+  <si>
+    <t>PRIMA RS COCKTL 450</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20015737</t>
+  </si>
+  <si>
+    <t>IDM NATA DE COCO 900</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>20028880</t>
+  </si>
+  <si>
+    <t>INACO NATA CRSPY 1KG</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>20125696</t>
+  </si>
+  <si>
+    <t>WG.C PUDING MANGO 3S</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
     <t>20139288</t>
   </si>
   <si>
     <t>LARISST COCOPANDN360</t>
   </si>
   <si>
-    <t>FES03N</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
+    <t>95</t>
   </si>
   <si>
     <t>20139289</t>
@@ -40,76 +769,16 @@
     <t>LARISST VANILLA 360G</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10000771</t>
-  </si>
-  <si>
-    <t>ABC SQUASH LECI 425</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10000700</t>
-  </si>
-  <si>
-    <t>ABC SQSH ORNGE 425ML</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20031487</t>
-  </si>
-  <si>
-    <t>BANGAU SYRUP PSNG620</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10032795</t>
-  </si>
-  <si>
-    <t>INDOFOOD SYR ORG 460</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10000704</t>
-  </si>
-  <si>
-    <t>MARJAN COCOPDN 460ML</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>10000772</t>
-  </si>
-  <si>
-    <t>MARJAN MELON 460ML</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20019631</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK 1L</t>
-  </si>
-  <si>
-    <t>41</t>
+    <t>96</t>
+  </si>
+  <si>
+    <t>20140229</t>
+  </si>
+  <si>
+    <t>W/COCO PUD BLUE3X120</t>
+  </si>
+  <si>
+    <t>97</t>
   </si>
 </sst>
 </file>
@@ -502,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -510,7 +1179,7 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -547,30 +1216,30 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -590,127 +1259,1587 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/FES03N.xlsx
+++ b/FES03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="262">
   <si>
     <t/>
   </si>
@@ -61,13 +61,31 @@
     <t>4</t>
   </si>
   <si>
+    <t>20122092</t>
+  </si>
+  <si>
+    <t>MRJAN SYRP LEMON 425</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10036619</t>
+  </si>
+  <si>
+    <t>MARJAN SRP LYCHE 425</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>10000700</t>
   </si>
   <si>
     <t>ABC SQSH ORNGE 425ML</t>
   </si>
   <si>
-    <t>5</t>
+    <t>7</t>
   </si>
   <si>
     <t>10000704</t>
@@ -76,7 +94,7 @@
     <t>MARJAN COCOPANDAN425</t>
   </si>
   <si>
-    <t>6</t>
+    <t>8</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
@@ -88,7 +106,7 @@
     <t>ABC SQUASH LECI 425</t>
   </si>
   <si>
-    <t>7</t>
+    <t>9</t>
   </si>
   <si>
     <t>10000772</t>
@@ -97,7 +115,7 @@
     <t>MARJAN MELON 425ML</t>
   </si>
   <si>
-    <t>8</t>
+    <t>10</t>
   </si>
   <si>
     <t>10010933</t>
@@ -106,7 +124,7 @@
     <t>MARJAN SYRP ORNG 375</t>
   </si>
   <si>
-    <t>9</t>
+    <t>11</t>
   </si>
   <si>
     <t>10010946</t>
@@ -115,7 +133,7 @@
     <t>MARJAN SQ.CCOPD 375</t>
   </si>
   <si>
-    <t>10</t>
+    <t>12</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -127,7 +145,7 @@
     <t>INDOFOOD SYR ORG 460</t>
   </si>
   <si>
-    <t>11</t>
+    <t>13</t>
   </si>
   <si>
     <t>10032797</t>
@@ -136,7 +154,7 @@
     <t>INDOFOOD SYR CCP 460</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>10036625</t>
@@ -145,7 +163,7 @@
     <t>ABC SG MELON 460</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>20005058</t>
@@ -154,7 +172,7 @@
     <t>FANTA FRUIT PUNCH1.5</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>20015819</t>
@@ -163,7 +181,7 @@
     <t>INDOFOOD SYR MLN 460</t>
   </si>
   <si>
-    <t>16</t>
+    <t>18</t>
   </si>
   <si>
     <t>20019631</t>
@@ -172,7 +190,7 @@
     <t>SOSRO TEH BTL TPK 1L</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>20066299</t>
@@ -181,7 +199,7 @@
     <t>MARJAN SQSH MLN 375</t>
   </si>
   <si>
-    <t>21</t>
+    <t>23</t>
   </si>
   <si>
     <t>20142239</t>
@@ -190,7 +208,7 @@
     <t>N/P MINUMAN LIME 1L</t>
   </si>
   <si>
-    <t>24</t>
+    <t>26</t>
   </si>
   <si>
     <t>20144280</t>
@@ -199,7 +217,7 @@
     <t>FANTA LECI 1500ML</t>
   </si>
   <si>
-    <t>25</t>
+    <t>27</t>
   </si>
   <si>
     <t>PT,(E-14H)</t>
@@ -211,7 +229,7 @@
     <t>KHONG GUAN MN ASS650</t>
   </si>
   <si>
-    <t>26</t>
+    <t>28</t>
   </si>
   <si>
     <t>10000360</t>
@@ -220,7 +238,7 @@
     <t>KHONG GUAN RED 1600G</t>
   </si>
   <si>
-    <t>27</t>
+    <t>29</t>
   </si>
   <si>
     <t>10000734</t>
@@ -229,7 +247,7 @@
     <t>NISSIN WFR CHOCO 570</t>
   </si>
   <si>
-    <t>28</t>
+    <t>30</t>
   </si>
   <si>
     <t>20010655</t>
@@ -238,7 +256,7 @@
     <t>TANGO WFER CHOCO 220</t>
   </si>
   <si>
-    <t>29</t>
+    <t>31</t>
   </si>
   <si>
     <t>20015239</t>
@@ -247,7 +265,7 @@
     <t>TANGO WAFER VNL 220</t>
   </si>
   <si>
-    <t>30</t>
+    <t>32</t>
   </si>
   <si>
     <t>20025285</t>
@@ -256,7 +274,7 @@
     <t>GERY BUTER COKIS 300</t>
   </si>
   <si>
-    <t>31</t>
+    <t>33</t>
   </si>
   <si>
     <t>20030644</t>
@@ -265,7 +283,7 @@
     <t>GERY EGG ROLL 210G</t>
   </si>
   <si>
-    <t>32</t>
+    <t>34</t>
   </si>
   <si>
     <t>20041251</t>
@@ -274,7 +292,7 @@
     <t>NABATI RCHSE WFR 226</t>
   </si>
   <si>
-    <t>33</t>
+    <t>35</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
@@ -286,7 +304,7 @@
     <t>NABATI RCHOC WFR 226</t>
   </si>
   <si>
-    <t>34</t>
+    <t>36</t>
   </si>
   <si>
     <t>20074001</t>
@@ -295,7 +313,7 @@
     <t>NEXTAR BROWNIES 126G</t>
   </si>
   <si>
-    <t>35</t>
+    <t>37</t>
   </si>
   <si>
     <t>20084959</t>
@@ -304,7 +322,7 @@
     <t>GERY CHOCLTS DARK190</t>
   </si>
   <si>
-    <t>36</t>
+    <t>38</t>
   </si>
   <si>
     <t>20133606</t>
@@ -313,7 +331,7 @@
     <t>GIZZI MILK WAFER240</t>
   </si>
   <si>
-    <t>37</t>
+    <t>39</t>
   </si>
   <si>
     <t>20140010</t>
@@ -322,7 +340,7 @@
     <t>GIZZI MLK WFR MKC240</t>
   </si>
   <si>
-    <t>38</t>
+    <t>40</t>
   </si>
   <si>
     <t>20040511</t>
@@ -331,7 +349,7 @@
     <t>NSSIN WFR CHO S/E200</t>
   </si>
   <si>
-    <t>39</t>
+    <t>41</t>
   </si>
   <si>
     <t>20137532</t>
@@ -340,7 +358,7 @@
     <t>TANGO WFR CHEESE 200</t>
   </si>
   <si>
-    <t>40</t>
+    <t>42</t>
   </si>
   <si>
     <t>10000132</t>
@@ -349,7 +367,7 @@
     <t>MONDE BT.COOKIES 454</t>
   </si>
   <si>
-    <t>41</t>
+    <t>43</t>
   </si>
   <si>
     <t>10000730</t>
@@ -358,7 +376,7 @@
     <t>ASTOR STICK CKLT 330</t>
   </si>
   <si>
-    <t>44</t>
+    <t>46</t>
   </si>
   <si>
     <t>10000735</t>
@@ -367,7 +385,7 @@
     <t>ROMA BISC KELAPA 345</t>
   </si>
   <si>
-    <t>45</t>
+    <t>47</t>
   </si>
   <si>
     <t>10005166</t>
@@ -376,7 +394,7 @@
     <t>FOX'S FRUITS 150G</t>
   </si>
   <si>
-    <t>46</t>
+    <t>48</t>
   </si>
   <si>
     <t>10036928</t>
@@ -385,7 +403,7 @@
     <t>MD.EGG ROLL MINI 300</t>
   </si>
   <si>
-    <t>47</t>
+    <t>49</t>
   </si>
   <si>
     <t>20015928</t>
@@ -394,7 +412,7 @@
     <t>HATARI BISCUIT 300G</t>
   </si>
   <si>
-    <t>50</t>
+    <t>52</t>
   </si>
   <si>
     <t>20015929</t>
@@ -403,7 +421,7 @@
     <t>HATARI BISC.ASS 650G</t>
   </si>
   <si>
-    <t>51</t>
+    <t>53</t>
   </si>
   <si>
     <t>20018270</t>
@@ -412,7 +430,7 @@
     <t>FOX'S BERRIES KLG150</t>
   </si>
   <si>
-    <t>53</t>
+    <t>55</t>
   </si>
   <si>
     <t>20020625</t>
@@ -421,7 +439,7 @@
     <t>G/T COOKIES 120G</t>
   </si>
   <si>
-    <t>54</t>
+    <t>56</t>
   </si>
   <si>
     <t>20023805</t>
@@ -430,7 +448,7 @@
     <t>INACO JELLY MINI 50S</t>
   </si>
   <si>
-    <t>55</t>
+    <t>57</t>
   </si>
   <si>
     <t>20031552</t>
@@ -439,7 +457,7 @@
     <t>GOOD FAMILY KLG 400G</t>
   </si>
   <si>
-    <t>56</t>
+    <t>58</t>
   </si>
   <si>
     <t>20036130</t>
@@ -448,7 +466,7 @@
     <t>ROCHO WFR BOLA 300G</t>
   </si>
   <si>
-    <t>57</t>
+    <t>59</t>
   </si>
   <si>
     <t>20036135</t>
@@ -457,7 +475,7 @@
     <t>IDM WAFER STICK 450G</t>
   </si>
   <si>
-    <t>58</t>
+    <t>60</t>
   </si>
   <si>
     <t>20069566</t>
@@ -466,7 +484,7 @@
     <t>HOCK GUAN BISC.1350G</t>
   </si>
   <si>
-    <t>59</t>
+    <t>61</t>
   </si>
   <si>
     <t>20069567</t>
@@ -475,7 +493,7 @@
     <t>CORONATION BISC.450G</t>
   </si>
   <si>
-    <t>60</t>
+    <t>62</t>
   </si>
   <si>
     <t>20074004</t>
@@ -484,7 +502,7 @@
     <t>BORNEO BISC KLG 300G</t>
   </si>
   <si>
-    <t>62</t>
+    <t>64</t>
   </si>
   <si>
     <t>20076737</t>
@@ -493,7 +511,7 @@
     <t>SERENA CHS COOK 454G</t>
   </si>
   <si>
-    <t>63</t>
+    <t>65</t>
   </si>
   <si>
     <t>20084963</t>
@@ -502,7 +520,7 @@
     <t>KG WAFER STK CHO 500</t>
   </si>
   <si>
-    <t>64</t>
+    <t>66</t>
   </si>
   <si>
     <t>20094206</t>
@@ -511,7 +529,7 @@
     <t>ROMA WAFELLO CHO 234</t>
   </si>
   <si>
-    <t>65</t>
+    <t>67</t>
   </si>
   <si>
     <t>20102838</t>
@@ -520,7 +538,7 @@
     <t>MONDE SLCT BISC 800G</t>
   </si>
   <si>
-    <t>66</t>
+    <t>68</t>
   </si>
   <si>
     <t>20103665</t>
@@ -529,7 +547,7 @@
     <t>KINO NASTAR PNPL120</t>
   </si>
   <si>
-    <t>67</t>
+    <t>69</t>
   </si>
   <si>
     <t>20112474</t>
@@ -538,7 +556,7 @@
     <t>NISSIN WALEN BIS600G</t>
   </si>
   <si>
-    <t>68</t>
+    <t>70</t>
   </si>
   <si>
     <t>20112570</t>
@@ -547,7 +565,7 @@
     <t>KOKOLA C/BUTTER 288</t>
   </si>
   <si>
-    <t>69</t>
+    <t>71</t>
   </si>
   <si>
     <t>20112571</t>
@@ -556,7 +574,7 @@
     <t>KOKOLA C/COCONUT 288</t>
   </si>
   <si>
-    <t>70</t>
+    <t>72</t>
   </si>
   <si>
     <t>20112572</t>
@@ -565,7 +583,7 @@
     <t>KOKOLA C/CHOCO 288G</t>
   </si>
   <si>
-    <t>71</t>
+    <t>73</t>
   </si>
   <si>
     <t>20119647</t>
@@ -574,7 +592,7 @@
     <t>RIA RIO CRM VNLA 400</t>
   </si>
   <si>
-    <t>73</t>
+    <t>75</t>
   </si>
   <si>
     <t>20119648</t>
@@ -583,7 +601,7 @@
     <t>ROMA WFLO B.CRML 228</t>
   </si>
   <si>
-    <t>74</t>
+    <t>76</t>
   </si>
   <si>
     <t>20125797</t>
@@ -592,7 +610,7 @@
     <t>CHO2 WR SMPRG K/W270</t>
   </si>
   <si>
-    <t>76</t>
+    <t>78</t>
   </si>
   <si>
     <t>20127567</t>
@@ -601,7 +619,7 @@
     <t>ROYAL/C COOKIES 240G</t>
   </si>
   <si>
-    <t>77</t>
+    <t>79</t>
   </si>
   <si>
     <t>20133029</t>
@@ -610,7 +628,7 @@
     <t>TANGO WFL CHO HZL150</t>
   </si>
   <si>
-    <t>78</t>
+    <t>80</t>
   </si>
   <si>
     <t>20133030</t>
@@ -619,7 +637,7 @@
     <t>ROMA ARDEN CHOCO 216</t>
   </si>
   <si>
-    <t>79</t>
+    <t>81</t>
   </si>
   <si>
     <t>20133031</t>
@@ -628,7 +646,7 @@
     <t>IMPERIAL ASSRTD 144G</t>
   </si>
   <si>
-    <t>80</t>
+    <t>82</t>
   </si>
   <si>
     <t>20136760</t>
@@ -637,7 +655,7 @@
     <t>ROMA SANDW CKLT 300G</t>
   </si>
   <si>
-    <t>82</t>
+    <t>84</t>
   </si>
   <si>
     <t>20140008</t>
@@ -646,7 +664,7 @@
     <t>OREO SPC FAMILY213.2</t>
   </si>
   <si>
-    <t>83</t>
+    <t>85</t>
   </si>
   <si>
     <t>20143784</t>
@@ -655,7 +673,7 @@
     <t>DELBIS DLCA C/CHO152</t>
   </si>
   <si>
-    <t>84</t>
+    <t>86</t>
   </si>
   <si>
     <t>20143861</t>
@@ -664,7 +682,7 @@
     <t>G/T MLK MCA DIP120.7</t>
   </si>
   <si>
-    <t>85</t>
+    <t>87</t>
   </si>
   <si>
     <t>20140953</t>
@@ -673,7 +691,7 @@
     <t>P100 BCKT COK K/H240</t>
   </si>
   <si>
-    <t>86</t>
+    <t>88</t>
   </si>
   <si>
     <t>20143575</t>
@@ -682,7 +700,7 @@
     <t>P100 BCKT KRM MD200</t>
   </si>
   <si>
-    <t>87</t>
+    <t>89</t>
   </si>
   <si>
     <t>20133363</t>
@@ -691,7 +709,7 @@
     <t>TANGO WFR MLK CHO220</t>
   </si>
   <si>
-    <t>88</t>
+    <t>90</t>
   </si>
   <si>
     <t>10020713</t>
@@ -700,7 +718,7 @@
     <t>WG COCO CUBE CP 1KG</t>
   </si>
   <si>
-    <t>89</t>
+    <t>91</t>
   </si>
   <si>
     <t>RT,(E-0.5B)</t>
@@ -712,7 +730,7 @@
     <t>W/COCO CCPD SLC 1KG</t>
   </si>
   <si>
-    <t>90</t>
+    <t>92</t>
   </si>
   <si>
     <t>10038354</t>
@@ -721,7 +739,7 @@
     <t>PRIMA RS COCKTL 450</t>
   </si>
   <si>
-    <t>91</t>
+    <t>93</t>
   </si>
   <si>
     <t>RT,(E-7H)</t>
@@ -733,7 +751,7 @@
     <t>IDM NATA DE COCO 900</t>
   </si>
   <si>
-    <t>92</t>
+    <t>94</t>
   </si>
   <si>
     <t>20028880</t>
@@ -742,7 +760,7 @@
     <t>INACO NATA CRSPY 1KG</t>
   </si>
   <si>
-    <t>93</t>
+    <t>95</t>
   </si>
   <si>
     <t>20125696</t>
@@ -751,7 +769,7 @@
     <t>WG.C PUDING MANGO 3S</t>
   </si>
   <si>
-    <t>94</t>
+    <t>96</t>
   </si>
   <si>
     <t>20139288</t>
@@ -760,7 +778,7 @@
     <t>LARISST COCOPANDN360</t>
   </si>
   <si>
-    <t>95</t>
+    <t>97</t>
   </si>
   <si>
     <t>20139289</t>
@@ -769,7 +787,7 @@
     <t>LARISST VANILLA 360G</t>
   </si>
   <si>
-    <t>96</t>
+    <t>98</t>
   </si>
   <si>
     <t>20140229</t>
@@ -778,7 +796,7 @@
     <t>W/COCO PUD BLUE3X120</t>
   </si>
   <si>
-    <t>97</t>
+    <t>99</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1319,24 +1337,24 @@
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -1344,22 +1362,22 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1379,7 +1397,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1399,47 +1417,47 @@
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1479,7 +1497,7 @@
         <v>47</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1499,7 +1517,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1519,7 +1537,7 @@
         <v>53</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1539,7 +1557,7 @@
         <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1559,7 +1577,7 @@
         <v>59</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1579,47 +1597,47 @@
         <v>62</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1639,7 +1657,7 @@
         <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1659,7 +1677,7 @@
         <v>75</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1679,7 +1697,7 @@
         <v>78</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1699,7 +1717,7 @@
         <v>81</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1719,7 +1737,7 @@
         <v>84</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1739,47 +1757,47 @@
         <v>87</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1799,7 +1817,7 @@
         <v>97</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1819,7 +1837,7 @@
         <v>100</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1839,7 +1857,7 @@
         <v>103</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1859,7 +1877,7 @@
         <v>106</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1879,7 +1897,7 @@
         <v>109</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1899,7 +1917,7 @@
         <v>112</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1919,7 +1937,7 @@
         <v>115</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1939,7 +1957,7 @@
         <v>118</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1959,7 +1977,7 @@
         <v>121</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1979,7 +1997,7 @@
         <v>124</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1999,7 +2017,7 @@
         <v>127</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2019,7 +2037,7 @@
         <v>130</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2039,7 +2057,7 @@
         <v>133</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2059,7 +2077,7 @@
         <v>136</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2079,7 +2097,7 @@
         <v>139</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2099,7 +2117,7 @@
         <v>142</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2119,7 +2137,7 @@
         <v>145</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,7 +2157,7 @@
         <v>148</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2159,7 +2177,7 @@
         <v>151</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,7 +2197,7 @@
         <v>154</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2219,7 +2237,7 @@
         <v>160</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2239,7 +2257,7 @@
         <v>163</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2259,7 +2277,7 @@
         <v>166</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2279,7 +2297,7 @@
         <v>169</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2299,7 +2317,7 @@
         <v>172</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2319,7 +2337,7 @@
         <v>175</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2339,7 +2357,7 @@
         <v>178</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2359,7 +2377,7 @@
         <v>181</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2399,7 +2417,7 @@
         <v>187</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2419,7 +2437,7 @@
         <v>190</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2439,7 +2457,7 @@
         <v>193</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2459,7 +2477,7 @@
         <v>196</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2479,7 +2497,7 @@
         <v>199</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,7 +2517,7 @@
         <v>202</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2519,7 +2537,7 @@
         <v>205</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2539,7 +2557,7 @@
         <v>208</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2559,7 +2577,7 @@
         <v>211</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2579,7 +2597,7 @@
         <v>214</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2599,7 +2617,7 @@
         <v>217</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2619,7 +2637,7 @@
         <v>220</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2639,7 +2657,7 @@
         <v>223</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2659,7 +2677,7 @@
         <v>226</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2679,87 +2697,87 @@
         <v>229</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>230</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>230</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2779,7 +2797,7 @@
         <v>246</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>230</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2799,7 +2817,7 @@
         <v>249</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2819,7 +2837,7 @@
         <v>252</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>35</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2839,7 +2857,47 @@
         <v>255</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>230</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
